--- a/INPUT-Incentive-mau.xlsx
+++ b/INPUT-Incentive-mau.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" r:id="R54d9e6a0400246d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân sự" sheetId="2" r:id="R06953e92d568455b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khách hàng" sheetId="3" r:id="R8c85a67f1c6f4d1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Công nợ chi tiết" sheetId="4" r:id="Rf8b6cf8b2a1a42b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" r:id="Ree1c7c8719ec4ff5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân sự" sheetId="2" r:id="R2b1c08e42dfa4dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khách hàng" sheetId="3" r:id="R102f3045d7e94764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Công nợ chi tiết" sheetId="4" r:id="R1b83b51f7f0d4316"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quy tắc phạt" sheetId="5" r:id="Rc6a83734ada64feb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,9 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="2">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="#,##0;[Red](#,##0);-"/>
     <x:numFmt numFmtId="201" formatCode="0.00%;[Red](0.00%);-"/>
+    <x:numFmt numFmtId="202" formatCode="0.0%"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -37,7 +39,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -49,14 +51,72 @@
         <x:fgColor rgb="FF44318D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4D358B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF8E1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4D358B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF8E1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4D358B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF8E1"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="3">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9D2E9"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9D2E9"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9D2E9"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9D2E9"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -99,6 +159,79 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -310,7 +443,7 @@
     <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12.15999984741211" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16.979999542236328" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11.199999809265137" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="0" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="21" customHeight="1">
@@ -338,9 +471,7 @@
       <x:c r="H1" s="4" t="str">
         <x:v>Trạng thái thu</x:v>
       </x:c>
-      <x:c r="I1" s="15" t="str">
-        <x:v>% đã thu</x:v>
-      </x:c>
+      <x:c r="I1"/>
     </x:row>
     <x:row r="2" ht="16.5" customHeight="1">
       <x:c r="A2" s="8" t="n">
@@ -359,7 +490,7 @@
         <x:v>Khách hàng 01</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G2" s="12" t="n">
         <x:v>17510000</x:v>
@@ -367,9 +498,7 @@
       <x:c r="H2" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I2" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I2"/>
     </x:row>
     <x:row r="3" ht="16.5" customHeight="1">
       <x:c r="A3" s="8" t="n">
@@ -388,7 +517,7 @@
         <x:v>Khách hàng 01</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G3" s="12" t="n">
         <x:v>16000000</x:v>
@@ -396,9 +525,7 @@
       <x:c r="H3" s="6" t="str">
         <x:v>Unpaid</x:v>
       </x:c>
-      <x:c r="I3" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I3"/>
     </x:row>
     <x:row r="4" ht="16.5" customHeight="1">
       <x:c r="A4" s="8" t="n">
@@ -417,7 +544,7 @@
         <x:v>Khách hàng 01</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G4" s="12" t="n">
         <x:v>17130000</x:v>
@@ -425,9 +552,7 @@
       <x:c r="H4" s="6" t="str">
         <x:v>Unpaid</x:v>
       </x:c>
-      <x:c r="I4" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I4"/>
     </x:row>
     <x:row r="5" ht="16.5" customHeight="1">
       <x:c r="A5" s="8" t="n">
@@ -446,7 +571,7 @@
         <x:v>Khách hàng 02</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G5" s="12" t="n">
         <x:v>4365248</x:v>
@@ -454,9 +579,7 @@
       <x:c r="H5" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I5" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I5"/>
     </x:row>
     <x:row r="6" ht="16.5" customHeight="1">
       <x:c r="A6" s="8" t="n">
@@ -475,7 +598,7 @@
         <x:v>Khách hàng 03</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G6" s="12" t="n">
         <x:v>11366042</x:v>
@@ -483,9 +606,7 @@
       <x:c r="H6" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I6" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I6"/>
     </x:row>
     <x:row r="7" ht="16.5" customHeight="1">
       <x:c r="A7" s="8" t="n">
@@ -504,7 +625,7 @@
         <x:v>Khách hàng 02</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G7" s="12" t="n">
         <x:v>3000000</x:v>
@@ -512,9 +633,7 @@
       <x:c r="H7" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I7" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I7"/>
     </x:row>
     <x:row r="8" ht="16.5" customHeight="1">
       <x:c r="A8" s="8" t="n">
@@ -533,7 +652,7 @@
         <x:v>Khách hàng 04</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G8" s="12" t="n">
         <x:v>24364808</x:v>
@@ -541,9 +660,7 @@
       <x:c r="H8" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I8" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I8"/>
     </x:row>
     <x:row r="9" ht="16.5" customHeight="1">
       <x:c r="A9" s="8" t="n">
@@ -562,7 +679,7 @@
         <x:v>Khách hàng 04</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G9" s="12" t="n">
         <x:v>12736198</x:v>
@@ -570,9 +687,7 @@
       <x:c r="H9" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I9" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I9"/>
     </x:row>
     <x:row r="10" ht="16.5" customHeight="1">
       <x:c r="A10" s="8" t="n">
@@ -591,7 +706,7 @@
         <x:v>Khách hàng 04</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G10" s="12" t="n">
         <x:v>101203445</x:v>
@@ -599,9 +714,7 @@
       <x:c r="H10" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I10" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I10"/>
     </x:row>
     <x:row r="11" ht="16.5" customHeight="1">
       <x:c r="A11" s="8" t="n">
@@ -620,7 +733,7 @@
         <x:v>Khách hàng 02</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
-        <x:v>COM</x:v>
+        <x:v>General</x:v>
       </x:c>
       <x:c r="G11" s="12" t="n">
         <x:v>25374836</x:v>
@@ -628,9 +741,7 @@
       <x:c r="H11" s="6" t="str">
         <x:v>Paid</x:v>
       </x:c>
-      <x:c r="I11" s="16" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="I11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -650,6 +761,8 @@
     <x:col min="7" max="7" width="15.050000190734863" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="21" customHeight="1">
@@ -680,6 +793,12 @@
       <x:c r="I1" s="4" t="str">
         <x:v>HĐLĐ</x:v>
       </x:c>
+      <x:c r="J1" s="36" t="str">
+        <x:v>Chỉ tiêu KH mới</x:v>
+      </x:c>
+      <x:c r="K1" s="36" t="str">
+        <x:v>KH mới đạt</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="16.5" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -708,6 +827,12 @@
       </x:c>
       <x:c r="I2" s="6" t="str">
         <x:v>Có</x:v>
+      </x:c>
+      <x:c r="J2" s="37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K2" s="37" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -776,6 +901,8 @@
     <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="20.829999923706055" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="21" customHeight="1">
@@ -791,6 +918,12 @@
       <x:c r="D1" s="7" t="str">
         <x:v>Số tháng quá hạn</x:v>
       </x:c>
+      <x:c r="E1" s="36" t="str">
+        <x:v>Team</x:v>
+      </x:c>
+      <x:c r="F1" s="36" t="str">
+        <x:v>Nhân tố phạt</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="16.5" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -805,6 +938,10 @@
       <x:c r="D2" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
+      <x:c r="E2" s="37" t="str">
+        <x:v>General</x:v>
+      </x:c>
+      <x:c r="F2" s="37" t="str"/>
     </x:row>
     <x:row r="3" ht="16.5" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -818,6 +955,97 @@
       </x:c>
       <x:c r="D3" s="8" t="n">
         <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str">
+        <x:v>General</x:v>
+      </x:c>
+      <x:c r="F3" s="37" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="52" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="36" t="str">
+        <x:v>Ưu tiên</x:v>
+      </x:c>
+      <x:c r="B1" s="36" t="str">
+        <x:v>Job</x:v>
+      </x:c>
+      <x:c r="C1" s="36" t="str">
+        <x:v>Team</x:v>
+      </x:c>
+      <x:c r="D1" s="36" t="str">
+        <x:v>Nhân tố phạt</x:v>
+      </x:c>
+      <x:c r="E1" s="36" t="str">
+        <x:v>Từ tháng quá hạn</x:v>
+      </x:c>
+      <x:c r="F1" s="36" t="str">
+        <x:v>Đến tháng quá hạn</x:v>
+      </x:c>
+      <x:c r="G1" s="36" t="str">
+        <x:v>Tỷ lệ phạt</x:v>
+      </x:c>
+      <x:c r="H1" s="36" t="str">
+        <x:v>Ghi chú</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="46" t="str">
+        <x:v>JOB-2PCT</x:v>
+      </x:c>
+      <x:c r="C2" s="46" t="str"/>
+      <x:c r="D2" s="46" t="str"/>
+      <x:c r="E2" s="45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="45" t="str"/>
+      <x:c r="G2" s="47" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="H2" s="46" t="str">
+        <x:v>Ví dụ 2% cho một job riêng. Thay hoặc xóa trước khi tính.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="45" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="46" t="str"/>
+      <x:c r="C3" s="46" t="str">
+        <x:v>TEAM-3PCT</x:v>
+      </x:c>
+      <x:c r="D3" s="46" t="str">
+        <x:v>NHAN_TO</x:v>
+      </x:c>
+      <x:c r="E3" s="45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="45" t="str"/>
+      <x:c r="G3" s="47" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="H3" s="46" t="str">
+        <x:v>Ví dụ 3% khi đủ Team, nhân tố và từ 3 tháng quá hạn.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
